--- a/hsk_core/resources/sheet/hsk1.xlsx
+++ b/hsk_core/resources/sheet/hsk1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Edmicro\Tools\Test\create_hsk\resources\sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Edmicro\Tools\create_hsk\hsk_core\resources\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8193F1EA-ABD5-447B-82E8-1E743322EEC8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E6753D-A741-430B-A784-06B877F4BF63}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ĐS (img) HSK1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="11">
   <si>
     <t>Đơn vị kiến thức
 &lt;Mã ĐVKT&gt;/&lt;Dạng bài&gt;</t>
@@ -82,15 +82,6 @@
   <si>
     <t>&lt;--- Viết link folder S3 chứa tài nguyên (ảnh, audio) vào ô này 
 Ví dụ: Tieng_Anh_tieu_hoc/LOP4</t>
-  </si>
-  <si>
-    <t>DS</t>
-  </si>
-  <si>
-    <t>NB</t>
-  </si>
-  <si>
-    <t>TN</t>
   </si>
 </sst>
 </file>
@@ -386,7 +377,7 @@
     <tabColor rgb="FF00FF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
@@ -440,38 +431,6 @@
       </c>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -484,7 +443,7 @@
     <tabColor rgb="FF00FF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
@@ -538,50 +497,6 @@
       </c>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -593,7 +508,7 @@
     <tabColor rgb="FF00FF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
@@ -647,50 +562,6 @@
       </c>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -702,7 +573,7 @@
     <tabColor rgb="FF00FF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
@@ -755,38 +626,6 @@
         <v>10</v>
       </c>
       <c r="M1" s="2"/>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -864,7 +703,7 @@
     <tabColor rgb="FF00FF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
@@ -918,50 +757,6 @@
       </c>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -973,7 +768,7 @@
     <tabColor rgb="FF00FF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
@@ -1027,50 +822,6 @@
       </c>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1082,7 +833,7 @@
     <tabColor rgb="FF00FF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
@@ -1136,50 +887,6 @@
       </c>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
